--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0003T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0003T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>82.0244438729591</v>
+        <v>13.32897212935585</v>
       </c>
       <c r="D2" t="n">
-        <v>78.39228605935867</v>
+        <v>12.73874648464578</v>
       </c>
       <c r="E2" t="n">
-        <v>14.77402586589191</v>
+        <v>2.400779203207436</v>
       </c>
       <c r="F2" t="n">
-        <v>17.82166668457554</v>
+        <v>2.896020836243526</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.31374579072406</v>
+        <v>7.363483690992661</v>
       </c>
       <c r="D3" t="n">
-        <v>41.68700815934108</v>
+        <v>6.774138825892926</v>
       </c>
       <c r="E3" t="n">
-        <v>14.77402586589191</v>
+        <v>2.400779203207436</v>
       </c>
       <c r="F3" t="n">
-        <v>17.82166668457554</v>
+        <v>2.896020836243526</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.03212592953247</v>
+        <v>7.967720463549027</v>
       </c>
       <c r="D4" t="n">
-        <v>45.48243178808008</v>
+        <v>7.390895165563013</v>
       </c>
       <c r="E4" t="n">
-        <v>14.77402586589191</v>
+        <v>2.400779203207436</v>
       </c>
       <c r="F4" t="n">
-        <v>17.82166668457554</v>
+        <v>2.896020836243526</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49.34481678072206</v>
+        <v>8.018532726867335</v>
       </c>
       <c r="D5" t="n">
-        <v>45.96656415838069</v>
+        <v>7.469566675736862</v>
       </c>
       <c r="E5" t="n">
-        <v>14.77402586589191</v>
+        <v>2.400779203207436</v>
       </c>
       <c r="F5" t="n">
-        <v>17.82166668457554</v>
+        <v>2.896020836243526</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.79773984200499</v>
+        <v>5.979632724325811</v>
       </c>
       <c r="D6" t="n">
-        <v>19.68622553009137</v>
+        <v>3.199011648639849</v>
       </c>
       <c r="E6" t="n">
-        <v>14.77402586589191</v>
+        <v>2.400779203207436</v>
       </c>
       <c r="F6" t="n">
-        <v>17.82166668457554</v>
+        <v>2.896020836243526</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.18023146843243</v>
+        <v>7.34178761362027</v>
       </c>
       <c r="D7" t="n">
-        <v>16.43075131169629</v>
+        <v>2.669997088150647</v>
       </c>
       <c r="E7" t="n">
-        <v>14.77402586589191</v>
+        <v>2.400779203207436</v>
       </c>
       <c r="F7" t="n">
-        <v>17.82166668457554</v>
+        <v>2.896020836243526</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.44991603289847</v>
+        <v>4.785611355346001</v>
       </c>
       <c r="D8" t="n">
-        <v>27.57291930171492</v>
+        <v>4.480599386528675</v>
       </c>
       <c r="E8" t="n">
-        <v>14.77402586589191</v>
+        <v>2.400779203207436</v>
       </c>
       <c r="F8" t="n">
-        <v>17.82166668457554</v>
+        <v>2.896020836243526</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>32.11507352870581</v>
+        <v>5.218699448414694</v>
       </c>
       <c r="D9" t="n">
-        <v>31.14242054046918</v>
+        <v>5.060643337826241</v>
       </c>
       <c r="E9" t="n">
-        <v>14.77402586589191</v>
+        <v>2.400779203207436</v>
       </c>
       <c r="F9" t="n">
-        <v>17.82166668457554</v>
+        <v>2.896020836243526</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>56.43971785720429</v>
+        <v>9.171454151795697</v>
       </c>
       <c r="D10" t="n">
-        <v>25.82422775298896</v>
+        <v>4.196437009860706</v>
       </c>
       <c r="E10" t="n">
-        <v>14.77402586589191</v>
+        <v>2.400779203207436</v>
       </c>
       <c r="F10" t="n">
-        <v>17.82166668457554</v>
+        <v>2.896020836243526</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
